--- a/codespace/DetroitRiverCase/results/ch4_fw2_pole_geometry_summary.xlsx
+++ b/codespace/DetroitRiverCase/results/ch4_fw2_pole_geometry_summary.xlsx
@@ -497,16 +497,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03455981471029238</v>
+        <v>-0.2881751473191632</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3473664733946803</v>
+        <v>0.2628556656999214</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1492628919313223</v>
+        <v>-0.1883836675010864</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06508454882931301</v>
+        <v>0.06985423492284636</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -515,7 +515,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.3792002519486574</v>
+        <v>0.6085406898020757</v>
       </c>
     </row>
     <row r="3">
@@ -525,29 +525,29 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3609344764829209</v>
+        <v>0.1890786221553013</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2083918575352792</v>
+        <v>-0.214280953227975</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1388144889785294</v>
+        <v>0.08631257098950422</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02804490063693696</v>
+        <v>0.02460827725324132</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3883844557467983</v>
+        <v>0.1454669777123019</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05489721765866932</v>
+        <v>-0.0228866130474508</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.6690411902682954</v>
+        <v>0.4414173744208198</v>
       </c>
     </row>
     <row r="4">
@@ -557,29 +557,29 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2506671582182178</v>
+        <v>0.2700779356081631</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.3040617138709271</v>
+        <v>-0.3343567958402198</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5811066950628524</v>
+        <v>-0.01765503330593833</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6809985611610924</v>
+        <v>0.0398508120756776</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1237704648803889</v>
+        <v>-0.08917365925216575</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3100717225771357</v>
+        <v>0.1244817036409572</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.5936418659943664</v>
+        <v>0.643658978751268</v>
       </c>
     </row>
   </sheetData>
